--- a/files/港岛-寿臣山及浅水湾-Shouson Peak.xlsx
+++ b/files/港岛-寿臣山及浅水湾-Shouson Peak.xlsx
@@ -111,7 +111,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -154,6 +154,12 @@
         <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E5E5E5"/>
+        <bgColor rgb="00E5E5E5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -181,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -232,6 +238,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -599,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2057,6 +2066,52 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>寿山村道19F号</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>4212</v>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>2017-05-01</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>376888000</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>89480</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
@@ -2072,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2126,22 +2181,22 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
+          <t>31 套</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>1 套</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
           <t>30 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>29 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -2496,6 +2551,27 @@
 $81,650/呎</t>
         </is>
       </c>
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>第 6 行</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道19F号
+4212呎 (4+房)
+(17年-05月-01日)
+$3.77亿
+$89,480/呎</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr"/>
+      <c r="D11" s="18" t="inlineStr"/>
+      <c r="E11" s="18" t="inlineStr"/>
+      <c r="F11" s="18" t="inlineStr"/>
+      <c r="G11" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/files/港岛-寿臣山及浅水湾-Shouson Peak.xlsx
+++ b/files/港岛-寿臣山及浅水湾-Shouson Peak.xlsx
@@ -111,7 +111,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -154,12 +154,6 @@
         <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -187,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -238,9 +232,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -608,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1701,7 +1692,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>寿山村道11G号</t>
+          <t>寿山村道19A号</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1720,7 +1711,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3601</v>
+        <v>3227</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -1729,14 +1720,14 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
+          <t>2013-12-17</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
-        <v>310128000</v>
+        <v>229898800</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>86123</v>
+        <v>71242</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -1747,7 +1738,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>寿山村道19A号</t>
+          <t>寿山村道19B号</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1766,7 +1757,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3227</v>
+        <v>3238</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -1775,14 +1766,14 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2013-12-17</t>
+          <t>2019-03-05</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
-        <v>229898800</v>
+        <v>240000000</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>71242</v>
+        <v>74120</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1784,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>寿山村道19B号</t>
+          <t>寿山村道19C号</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1821,14 +1812,14 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2019-03-05</t>
+          <t>2014-11-10</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
-        <v>240000000</v>
+        <v>238108000</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>74120</v>
+        <v>73536</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -1839,7 +1830,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>寿山村道19C号</t>
+          <t>寿山村道19D号</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1867,14 +1858,14 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2014-11-10</t>
+          <t>2014-01-02</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>238108000</v>
+        <v>231278800</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>73536</v>
+        <v>71426</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -1885,7 +1876,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>寿山村道19D号</t>
+          <t>寿山村道19E号</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1904,7 +1895,7 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3238</v>
+        <v>3212</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -1913,14 +1904,14 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2014-01-02</t>
+          <t>2018-05-09</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>231278800</v>
+        <v>262260000</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>71426</v>
+        <v>81650</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -1931,7 +1922,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>寿山村道19E号</t>
+          <t>寿山村道17A号</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1950,7 +1941,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3212</v>
+        <v>2989</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -1959,14 +1950,14 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2018-05-09</t>
+          <t>2012-04-26</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
-        <v>262260000</v>
+        <v>208000000</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>81650</v>
+        <v>69588</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -1977,7 +1968,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>寿山村道17A号</t>
+          <t>寿山村道9号</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1996,7 +1987,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2989</v>
+        <v>4271</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -2005,14 +1996,14 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2012-04-26</t>
+          <t>2016-08-15</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
-        <v>208000000</v>
+        <v>388000000</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>69588</v>
+        <v>90845</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -2023,7 +2014,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>寿山村道9号</t>
+          <t>寿山村道19F号</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2042,7 +2033,7 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>4271</v>
+        <v>4212</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -2051,62 +2042,16 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2016-08-15</t>
+          <t>2017-05-01</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
-        <v>388000000</v>
+        <v>376888000</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>90845</v>
+        <v>89480</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>寿山村道19F号</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>4212</v>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>2017-05-01</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>376888000</v>
-      </c>
-      <c r="I33" s="5" t="n">
-        <v>89480</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -2127,7 +2072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2181,7 +2126,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>31 套</t>
+          <t>30 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -2196,7 +2141,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>30 套</t>
+          <t>29 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -2325,15 +2270,6 @@
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>寿山村道11G号
-3601呎 (4+房)
-(21年-06月-07日)
-$3.10亿
-$86,123/呎</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
           <t>寿山村道15号
 4111呎 (4+房)
 (11年-01月-31日)
@@ -2341,7 +2277,7 @@
 $68,791/呎</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>寿山村道17A号
 2989呎 (4+房)
@@ -2350,7 +2286,7 @@
 $69,588/呎</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>寿山村道17B号
 2834呎 (4+房)
@@ -2359,7 +2295,7 @@
 $66,267/呎</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>寿山村道17C号
 2736呎 (4+房)
@@ -2368,14 +2304,7 @@
 $66,082/呎</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="80" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>第 3 行</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>寿山村道17D号
 2893呎 (4+房)
@@ -2384,7 +2313,14 @@
 $66,644/呎</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+    </row>
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>第 3 行</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>寿山村道17E号
 2953呎 (4+房)
@@ -2393,7 +2329,7 @@
 $69,421/呎</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>寿山村道17F号
 2927呎 (4+房)
@@ -2402,7 +2338,7 @@
 $72,087/呎</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>寿山村道17G号
 2927呎 (4+房)
@@ -2411,7 +2347,7 @@
 $78,039/呎</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>寿山村道17H号
 2908呎 (4+房)
@@ -2420,7 +2356,7 @@
 -</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>寿山村道17J号
 2897呎 (4+房)
@@ -2429,14 +2365,7 @@
 $44,460/呎</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="80" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>第 4 行</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>寿山村道17K号
 2950呎 (4+房)
@@ -2445,7 +2374,14 @@
 $42,372/呎</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+    </row>
+    <row r="9" ht="80" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>第 4 行</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>寿山村道17L号
 2948呎 (4+房)
@@ -2454,7 +2390,7 @@
 $43,073/呎</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>寿山村道17M号
 2967呎 (4+房)
@@ -2463,7 +2399,7 @@
 $45,056/呎</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>寿山村道17N号
 2755呎 (4+房)
@@ -2472,7 +2408,7 @@
 $70,628/呎</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>寿山村道17P号
 2733呎 (4+房)
@@ -2481,7 +2417,7 @@
 $55,121/呎</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>寿山村道17Q号
 2719呎 (4+房)
@@ -2490,14 +2426,7 @@
 $43,063/呎</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="80" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>第 5 行</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>寿山村道17R号
 2801呎 (4+房)
@@ -2506,7 +2435,14 @@
 $65,166/呎</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>第 5 行</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>寿山村道19A号
 3227呎 (4+房)
@@ -2515,7 +2451,7 @@
 $71,242/呎</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>寿山村道19B号
 3238呎 (4+房)
@@ -2524,7 +2460,7 @@
 $74,120/呎</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>寿山村道19C号
 3238呎 (4+房)
@@ -2533,7 +2469,7 @@
 $73,536/呎</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>寿山村道19D号
 3238呎 (4+房)
@@ -2542,7 +2478,7 @@
 $71,426/呎</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>寿山村道19E号
 3212呎 (4+房)
@@ -2551,14 +2487,7 @@
 $81,650/呎</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="80" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>第 6 行</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>寿山村道19F号
 4212呎 (4+房)
@@ -2567,11 +2496,6 @@
 $89,480/呎</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr"/>
-      <c r="D11" s="18" t="inlineStr"/>
-      <c r="E11" s="18" t="inlineStr"/>
-      <c r="F11" s="18" t="inlineStr"/>
-      <c r="G11" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/files/港岛-寿臣山及浅水湾-Shouson Peak.xlsx
+++ b/files/港岛-寿臣山及浅水湾-Shouson Peak.xlsx
@@ -111,7 +111,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -154,6 +154,12 @@
         <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E5E5E5"/>
+        <bgColor rgb="00E5E5E5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -181,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -232,6 +238,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -599,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1692,7 +1701,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>寿山村道19A号</t>
+          <t>寿山村道11G号</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1711,7 +1720,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3227</v>
+        <v>3601</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -1720,14 +1729,14 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2013-12-17</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
-        <v>229898800</v>
+        <v>310128000</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>71242</v>
+        <v>86123</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -1738,7 +1747,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>寿山村道19B号</t>
+          <t>寿山村道19A号</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1757,7 +1766,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3238</v>
+        <v>3227</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -1766,14 +1775,14 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2019-03-05</t>
+          <t>2013-12-17</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
-        <v>240000000</v>
+        <v>229898800</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>74120</v>
+        <v>71242</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -1784,7 +1793,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>寿山村道19C号</t>
+          <t>寿山村道19B号</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1812,14 +1821,14 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2014-11-10</t>
+          <t>2019-03-05</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
-        <v>238108000</v>
+        <v>240000000</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>73536</v>
+        <v>74120</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -1830,7 +1839,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>寿山村道19D号</t>
+          <t>寿山村道19C号</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1858,14 +1867,14 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2014-01-02</t>
+          <t>2014-11-10</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>231278800</v>
+        <v>238108000</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>71426</v>
+        <v>73536</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -1876,7 +1885,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>寿山村道19E号</t>
+          <t>寿山村道19D号</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1895,7 +1904,7 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3212</v>
+        <v>3238</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -1904,14 +1913,14 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2018-05-09</t>
+          <t>2014-01-02</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>262260000</v>
+        <v>231278800</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>81650</v>
+        <v>71426</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -1922,7 +1931,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>寿山村道17A号</t>
+          <t>寿山村道19E号</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1941,7 +1950,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2989</v>
+        <v>3212</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -1950,14 +1959,14 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2012-04-26</t>
+          <t>2018-05-09</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
-        <v>208000000</v>
+        <v>262260000</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>69588</v>
+        <v>81650</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -1968,7 +1977,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>寿山村道9号</t>
+          <t>寿山村道17A号</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1987,7 +1996,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4271</v>
+        <v>2989</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -1996,14 +2005,14 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2016-08-15</t>
+          <t>2012-04-26</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
-        <v>388000000</v>
+        <v>208000000</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>90845</v>
+        <v>69588</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -2014,44 +2023,90 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
+          <t>寿山村道9号</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>4271</v>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>2016-08-15</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>388000000</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>90845</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
           <t>寿山村道19F号</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="n">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="n">
         <v>4212</v>
       </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>2017-05-01</t>
         </is>
       </c>
-      <c r="H32" s="5" t="n">
+      <c r="H33" s="5" t="n">
         <v>376888000</v>
       </c>
-      <c r="I32" s="5" t="n">
+      <c r="I33" s="5" t="n">
         <v>89480</v>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -2072,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2126,22 +2181,22 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
+          <t>31 套</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>1 套</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
           <t>30 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>29 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -2270,6 +2325,15 @@
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
+          <t>寿山村道11G号
+3601呎 (4+房)
+(21年-06月-07日)
+$3.10亿
+$86,123/呎</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
           <t>寿山村道15号
 4111呎 (4+房)
 (11年-01月-31日)
@@ -2277,7 +2341,7 @@
 $68,791/呎</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>寿山村道17A号
 2989呎 (4+房)
@@ -2286,7 +2350,7 @@
 $69,588/呎</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>寿山村道17B号
 2834呎 (4+房)
@@ -2295,7 +2359,7 @@
 $66,267/呎</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>寿山村道17C号
 2736呎 (4+房)
@@ -2304,7 +2368,14 @@
 $66,082/呎</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+    </row>
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>第 3 行</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>寿山村道17D号
 2893呎 (4+房)
@@ -2313,14 +2384,7 @@
 $66,644/呎</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="80" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>第 3 行</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>寿山村道17E号
 2953呎 (4+房)
@@ -2329,7 +2393,7 @@
 $69,421/呎</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>寿山村道17F号
 2927呎 (4+房)
@@ -2338,7 +2402,7 @@
 $72,087/呎</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>寿山村道17G号
 2927呎 (4+房)
@@ -2347,7 +2411,7 @@
 $78,039/呎</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>寿山村道17H号
 2908呎 (4+房)
@@ -2356,7 +2420,7 @@
 -</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>寿山村道17J号
 2897呎 (4+房)
@@ -2365,7 +2429,14 @@
 $44,460/呎</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+    </row>
+    <row r="9" ht="80" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>第 4 行</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>寿山村道17K号
 2950呎 (4+房)
@@ -2374,14 +2445,7 @@
 $42,372/呎</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="80" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>第 4 行</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>寿山村道17L号
 2948呎 (4+房)
@@ -2390,7 +2454,7 @@
 $43,073/呎</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>寿山村道17M号
 2967呎 (4+房)
@@ -2399,7 +2463,7 @@
 $45,056/呎</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>寿山村道17N号
 2755呎 (4+房)
@@ -2408,7 +2472,7 @@
 $70,628/呎</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>寿山村道17P号
 2733呎 (4+房)
@@ -2417,7 +2481,7 @@
 $55,121/呎</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>寿山村道17Q号
 2719呎 (4+房)
@@ -2426,7 +2490,14 @@
 $43,063/呎</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>第 5 行</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>寿山村道17R号
 2801呎 (4+房)
@@ -2435,14 +2506,7 @@
 $65,166/呎</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="80" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>第 5 行</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>寿山村道19A号
 3227呎 (4+房)
@@ -2451,7 +2515,7 @@
 $71,242/呎</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>寿山村道19B号
 3238呎 (4+房)
@@ -2460,7 +2524,7 @@
 $74,120/呎</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>寿山村道19C号
 3238呎 (4+房)
@@ -2469,7 +2533,7 @@
 $73,536/呎</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>寿山村道19D号
 3238呎 (4+房)
@@ -2478,7 +2542,7 @@
 $71,426/呎</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>寿山村道19E号
 3212呎 (4+房)
@@ -2487,7 +2551,14 @@
 $81,650/呎</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>第 6 行</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>寿山村道19F号
 4212呎 (4+房)
@@ -2496,6 +2567,11 @@
 $89,480/呎</t>
         </is>
       </c>
+      <c r="C11" s="18" t="inlineStr"/>
+      <c r="D11" s="18" t="inlineStr"/>
+      <c r="E11" s="18" t="inlineStr"/>
+      <c r="F11" s="18" t="inlineStr"/>
+      <c r="G11" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/files/港岛-寿臣山及浅水湾-Shouson Peak.xlsx
+++ b/files/港岛-寿臣山及浅水湾-Shouson Peak.xlsx
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>4111</v>
+        <v>4144</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>282800000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>68791</v>
+        <v>68243</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2834</v>
+        <v>2713</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>187800000</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>66267</v>
+        <v>69222</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2736</v>
+        <v>2744</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>180800000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>66082</v>
+        <v>65889</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2893</v>
+        <v>2775</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>192800000</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>66644</v>
+        <v>69477</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2953</v>
+        <v>2957</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>205000000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>69421</v>
+        <v>69327</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2927</v>
+        <v>2932</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>211000000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>72087</v>
+        <v>71965</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2755</v>
+        <v>2760</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>194580000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>70628</v>
+        <v>70500</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2733</v>
+        <v>2739</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>150645000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>55121</v>
+        <v>55000</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2719</v>
+        <v>2723</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>117089000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>43063</v>
+        <v>43000</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2801</v>
+        <v>2808</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>182530000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>65166</v>
+        <v>65004</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2927</v>
+        <v>2931</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>228420000</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>78039</v>
+        <v>77932</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2908</v>
+        <v>2912</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2897</v>
+        <v>2901</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>128800000</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>44460</v>
+        <v>44398</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2950</v>
+        <v>2955</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>124996500</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>42372</v>
+        <v>42300</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2948</v>
+        <v>2953</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>126979000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>43073</v>
+        <v>43000</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2967</v>
+        <v>2972</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>133680000</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>45056</v>
+        <v>44980</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3602</v>
+        <v>3601</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>295282000</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>81977</v>
+        <v>82000</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3601</v>
+        <v>3600</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>180000000</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>49986</v>
+        <v>50000</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3605</v>
+        <v>3603</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>264766200</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>73444</v>
+        <v>73485</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3606</v>
+        <v>3603</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>262836500</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>72889</v>
+        <v>72949</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3567</v>
+        <v>3561</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>283500000</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>79479</v>
+        <v>79612</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3601</v>
+        <v>3603</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>310128000</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>86123</v>
+        <v>86075</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3212</v>
+        <v>3218</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>262260000</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>81650</v>
+        <v>81498</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2989</v>
+        <v>2986</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>208000000</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>69588</v>
+        <v>69658</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>4212</v>
+        <v>4237</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>376888000</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>89480</v>
+        <v>88952</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2274,37 +2274,37 @@
       <c r="D6" s="16" t="inlineStr">
         <is>
           <t>寿山村道11B号
-3602呎 (4+房)
+3601呎 (4+房)
 (21年-06月-09日)
 $2.95亿
-$81,977/呎</t>
+$82,000/呎</t>
         </is>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
           <t>寿山村道11C号
-3601呎 (4+房)
+3600呎 (4+房)
 (26年-02月-22日)
 $1.80亿
-$49,986/呎</t>
+$50,000/呎</t>
         </is>
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
           <t>寿山村道11D号
-3605呎 (4+房)
+3603呎 (4+房)
 (16年-06月-13日)
 $2.65亿
-$73,444/呎</t>
+$73,485/呎</t>
         </is>
       </c>
       <c r="G6" s="16" t="inlineStr">
         <is>
           <t>寿山村道11E号
-3606呎 (4+房)
+3603呎 (4+房)
 (13年-12月-16日)
 $2.63亿
-$72,889/呎</t>
+$72,949/呎</t>
         </is>
       </c>
     </row>
@@ -2317,55 +2317,55 @@
       <c r="B7" s="16" t="inlineStr">
         <is>
           <t>寿山村道11F号
-3567呎 (4+房)
+3561呎 (4+房)
 (17年-04月-17日)
 $2.83亿
-$79,479/呎</t>
+$79,612/呎</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
           <t>寿山村道11G号
-3601呎 (4+房)
+3603呎 (4+房)
 (21年-06月-07日)
 $3.10亿
-$86,123/呎</t>
+$86,075/呎</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
           <t>寿山村道15号
-4111呎 (4+房)
+4144呎 (4+房)
 (11年-01月-31日)
 $2.83亿
-$68,791/呎</t>
+$68,243/呎</t>
         </is>
       </c>
       <c r="E7" s="16" t="inlineStr">
         <is>
           <t>寿山村道17A号
-2989呎 (4+房)
+2986呎 (4+房)
 (12年-04月-26日)
 $2.08亿
-$69,588/呎</t>
+$69,658/呎</t>
         </is>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
           <t>寿山村道17B号
-2834呎 (4+房)
+2713呎 (4+房)
 (11年-07月-03日)
 $1.88亿
-$66,267/呎</t>
+$69,222/呎</t>
         </is>
       </c>
       <c r="G7" s="16" t="inlineStr">
         <is>
           <t>寿山村道17C号
-2736呎 (4+房)
+2744呎 (4+房)
 (11年-05月-31日)
 $1.81亿
-$66,082/呎</t>
+$65,889/呎</t>
         </is>
       </c>
     </row>
@@ -2378,43 +2378,43 @@
       <c r="B8" s="16" t="inlineStr">
         <is>
           <t>寿山村道17D号
-2893呎 (4+房)
+2775呎 (4+房)
 (12年-04月-19日)
 $1.93亿
-$66,644/呎</t>
+$69,477/呎</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
           <t>寿山村道17E号
-2953呎 (4+房)
+2957呎 (4+房)
 (11年-06月-21日)
 $2.05亿
-$69,421/呎</t>
+$69,327/呎</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
           <t>寿山村道17F号
-2927呎 (4+房)
+2932呎 (4+房)
 (12年-12月-05日)
 $2.11亿
-$72,087/呎</t>
+$71,965/呎</t>
         </is>
       </c>
       <c r="E8" s="16" t="inlineStr">
         <is>
           <t>寿山村道17G号
-2927呎 (4+房)
+2931呎 (4+房)
 (16年-10月-31日)
 $2.28亿
-$78,039/呎</t>
+$77,932/呎</t>
         </is>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
           <t>寿山村道17H号
-2908呎 (4+房)
+2912呎 (4+房)
 (在售)
 招标项目
 -</t>
@@ -2423,10 +2423,10 @@
       <c r="G8" s="16" t="inlineStr">
         <is>
           <t>寿山村道17J号
-2897呎 (4+房)
+2901呎 (4+房)
 (25年-06月-18日)
 $1.29亿
-$44,460/呎</t>
+$44,398/呎</t>
         </is>
       </c>
     </row>
@@ -2439,55 +2439,55 @@
       <c r="B9" s="16" t="inlineStr">
         <is>
           <t>寿山村道17K号
-2950呎 (4+房)
+2955呎 (4+房)
 (25年-07月-03日)
 $1.25亿
-$42,372/呎</t>
+$42,300/呎</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
           <t>寿山村道17L号
-2948呎 (4+房)
+2953呎 (4+房)
 (25年-08月-27日)
 $1.27亿
-$43,073/呎</t>
+$43,000/呎</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
           <t>寿山村道17M号
-2967呎 (4+房)
+2972呎 (4+房)
 (25年-09月-18日)
 $1.34亿
-$45,056/呎</t>
+$44,980/呎</t>
         </is>
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
           <t>寿山村道17N号
-2755呎 (4+房)
+2760呎 (4+房)
 (21年-06月-22日)
 $1.95亿
-$70,628/呎</t>
+$70,500/呎</t>
         </is>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
           <t>寿山村道17P号
-2733呎 (4+房)
+2739呎 (4+房)
 (26年-05月-27日)
 $1.51亿
-$55,121/呎</t>
+$55,000/呎</t>
         </is>
       </c>
       <c r="G9" s="16" t="inlineStr">
         <is>
           <t>寿山村道17Q号
-2719呎 (4+房)
+2723呎 (4+房)
 (25年-08月-28日)
 $1.17亿
-$43,063/呎</t>
+$43,000/呎</t>
         </is>
       </c>
     </row>
@@ -2500,10 +2500,10 @@
       <c r="B10" s="16" t="inlineStr">
         <is>
           <t>寿山村道17R号
-2801呎 (4+房)
+2808呎 (4+房)
 (26年-06月-16日)
 $1.83亿
-$65,166/呎</t>
+$65,004/呎</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -2545,10 +2545,10 @@
       <c r="G10" s="16" t="inlineStr">
         <is>
           <t>寿山村道19E号
-3212呎 (4+房)
+3218呎 (4+房)
 (18年-05月-09日)
 $2.62亿
-$81,650/呎</t>
+$81,498/呎</t>
         </is>
       </c>
     </row>
@@ -2561,10 +2561,10 @@
       <c r="B11" s="16" t="inlineStr">
         <is>
           <t>寿山村道19F号
-4212呎 (4+房)
+4237呎 (4+房)
 (17年-05月-01日)
 $3.77亿
-$89,480/呎</t>
+$88,952/呎</t>
         </is>
       </c>
       <c r="C11" s="18" t="inlineStr"/>
